--- a/data/trans_orig/P19C11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20254</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39333</t>
+          <t>40049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>18951</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32683</t>
+          <t>32640</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66900</t>
+          <t>67147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571971</t>
+          <t>571255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>591050</t>
+          <t>590929</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618849</t>
+          <t>618892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632103</t>
+          <t>632581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1195936</t>
+          <t>1195689</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219460</t>
+          <t>1219481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>17390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49300</t>
+          <t>50898</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29513</t>
+          <t>29321</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49428</t>
+          <t>49026</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48482</t>
+          <t>48052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>91387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1117416</t>
+          <t>1115818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1150218</t>
+          <t>1149326</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892897</t>
+          <t>893299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>912812</t>
+          <t>913004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2018987</t>
+          <t>2017653</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2060558</t>
+          <t>2060988</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46219</t>
+          <t>46033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15442</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46818</t>
+          <t>48252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>41442</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84276</t>
+          <t>84298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640048</t>
+          <t>640234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>663075</t>
+          <t>662546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>875235</t>
+          <t>873801</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>906611</t>
+          <t>906915</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1524044</t>
+          <t>1524022</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1567606</t>
+          <t>1566878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59137</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72742</t>
+          <t>71425</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>105713</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830798</t>
+          <t>831279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855187</t>
+          <t>855911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007646</t>
+          <t>1007822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030649</t>
+          <t>1030494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1847932</t>
+          <t>1847138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1880109</t>
+          <t>1881426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111338</t>
+          <t>105752</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168678</t>
+          <t>163532</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113688</t>
+          <t>112396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>160699</t>
+          <t>161142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236545</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314939</t>
+          <t>314375</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3185543</t>
+          <t>3190689</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3242883</t>
+          <t>3248469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3418128</t>
+          <t>3417685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3465139</t>
+          <t>3466431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6618109</t>
+          <t>6618673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6696503</t>
+          <t>6693508</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C11_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>30272</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20375</t>
+          <t>20727</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>41110</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>25341</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32640</t>
+          <t>37418</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,17 +795,17 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>53921</t>
+          <t>58334</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43355</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67147</t>
+          <t>71479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>582724</t>
+          <t>629259</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571255</t>
+          <t>618421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>590929</t>
+          <t>638804</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>626191</t>
+          <t>678087</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618892</t>
+          <t>668731</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>632581</t>
+          <t>684806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1208915</t>
+          <t>1307346</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1195689</t>
+          <t>1294201</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1219481</t>
+          <t>1319291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33572</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50898</t>
+          <t>49588</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38086</t>
+          <t>39536</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>31012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49026</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>76766</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48052</t>
+          <t>62849</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91387</t>
+          <t>96503</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1133144</t>
+          <t>978950</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1115818</t>
+          <t>966592</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1149326</t>
+          <t>990549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>904239</t>
+          <t>1008248</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>893299</t>
+          <t>996393</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>913004</t>
+          <t>1016772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2037383</t>
+          <t>1987198</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2017653</t>
+          <t>1967461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2060988</t>
+          <t>2001115</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33281</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>23721</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>46033</t>
+          <t>57395</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>39564</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>30192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48252</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>66205</t>
+          <t>80816</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>64196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84298</t>
+          <t>98889</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>652986</t>
+          <t>732757</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>640234</t>
+          <t>716613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>662546</t>
+          <t>744394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>889129</t>
+          <t>755781</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>873801</t>
+          <t>743466</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>906915</t>
+          <t>765153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1542115</t>
+          <t>1488537</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1524022</t>
+          <t>1470464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1566878</t>
+          <t>1505157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45242</t>
+          <t>46508</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34024</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58656</t>
+          <t>60609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42562</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>35693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55095</t>
+          <t>57034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>87803</t>
+          <t>91489</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>77761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105713</t>
+          <t>108945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>844693</t>
+          <t>901451</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>831279</t>
+          <t>887350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>855911</t>
+          <t>912085</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1020355</t>
+          <t>1031189</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007822</t>
+          <t>1019136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1030494</t>
+          <t>1040477</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1865048</t>
+          <t>1932640</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1847138</t>
+          <t>1915184</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1881426</t>
+          <t>1946368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105752</t>
+          <t>133792</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163532</t>
+          <t>180390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>138912</t>
+          <t>152143</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>112396</t>
+          <t>134476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161142</t>
+          <t>173205</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>279587</t>
+          <t>307405</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>239540</t>
+          <t>279706</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>314375</t>
+          <t>341573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3213547</t>
+          <t>3242416</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3190689</t>
+          <t>3217288</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3248469</t>
+          <t>3263886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3439915</t>
+          <t>3473305</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3417685</t>
+          <t>3452243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3466431</t>
+          <t>3490972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6653461</t>
+          <t>6715720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6618673</t>
+          <t>6681552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6693508</t>
+          <t>6743419</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
